--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487028_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487028_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7391</v>
+        <v>4.6255</v>
       </c>
       <c r="E2" t="n">
-        <v>3.825</v>
+        <v>3.6817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9142</v>
+        <v>0.9438</v>
       </c>
       <c r="G2" t="n">
         <v>0.3118</v>
@@ -610,13 +610,13 @@
         <v>1.2321</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4459</v>
+        <v>0.3322</v>
       </c>
       <c r="T2" t="n">
-        <v>0.612</v>
+        <v>0.4686</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1661</v>
+        <v>-0.1364</v>
       </c>
       <c r="V2" t="n">
         <v>3.7761</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.666</v>
+        <v>3.0119</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3248</v>
+        <v>3.066</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6587</v>
+        <v>-0.0541</v>
       </c>
       <c r="G3" t="n">
-        <v>3.52</v>
+        <v>3.456</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8764</v>
+        <v>0.9406</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3964</v>
+        <v>2.5155</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7739</v>
+        <v>2.9266</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5645</v>
+        <v>0.9928</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2094</v>
+        <v>1.9338</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2539</v>
+        <v>0.5294</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4409</v>
+        <v>-0.0522</v>
       </c>
       <c r="O3" t="n">
-        <v>0.187</v>
+        <v>0.5816</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1735</v>
+        <v>-0.1046</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2171</v>
+        <v>0.1394</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0436</v>
+        <v>-0.244</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2965</v>
+        <v>-1.777</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2965</v>
+        <v>-1.777</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3923</v>
+        <v>2.6747</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5051</v>
+        <v>4.6097</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1128</v>
+        <v>-1.935</v>
       </c>
       <c r="G4" t="n">
         <v>1.3741</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.606</v>
+        <v>-0.3236</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1435</v>
+        <v>-0.0389</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4625</v>
+        <v>-0.2846</v>
       </c>
       <c r="V4" t="n">
         <v>1.4189</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0952</v>
+        <v>2.5335</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2679</v>
+        <v>3.4294</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1727</v>
+        <v>-0.8959</v>
       </c>
       <c r="G5" t="n">
-        <v>3.456</v>
+        <v>3.52</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9406</v>
+        <v>-0.8764</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5155</v>
+        <v>4.3964</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9266</v>
+        <v>4.7739</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9928</v>
+        <v>0.5645</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9338</v>
+        <v>4.2094</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5294</v>
+        <v>-1.2539</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0522</v>
+        <v>-1.4409</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5816</v>
+        <v>0.187</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0213</v>
+        <v>-0.3061</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6587</v>
+        <v>-0.1125</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3625</v>
+        <v>-0.1936</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.777</v>
+        <v>-1.2965</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.777</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SALO BLAYA</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6622</v>
+        <v>-0.9889</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0183</v>
+        <v>-0.3635</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6806</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5002</v>
+        <v>-0.4108</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-1.9079</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5843</v>
+        <v>1.497</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6966</v>
+        <v>1.5244</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5782</v>
+        <v>-0.1328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1184</v>
+        <v>1.6572</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1963</v>
+        <v>-1.9352</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6623</v>
+        <v>-1.775</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4659</v>
+        <v>-0.1602</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9554</v>
+        <v>-0.2906</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3752</v>
+        <v>0.0424</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4198</v>
+        <v>-0.333</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2965</v>
+        <v>-0.6982</v>
       </c>
       <c r="W6" t="n">
+        <v>-0.6982</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-1.2965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>P. SALO BLAYA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7937</v>
+        <v>-1.8656</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0497</v>
+        <v>-1.0664</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.744</v>
+        <v>-0.7991</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4108</v>
+        <v>0.5002</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9079</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.497</v>
+        <v>0.5843</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5244</v>
+        <v>0.6966</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1328</v>
+        <v>0.5782</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6572</v>
+        <v>0.1184</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9352</v>
+        <v>-0.1963</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.775</v>
+        <v>-0.6623</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1602</v>
+        <v>0.4659</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0954</v>
+        <v>-0.2479</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3562</v>
+        <v>0.2904</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4516</v>
+        <v>-0.5384</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6982</v>
+        <v>-1.2965</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6694</v>
+        <v>-2.0128</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6515</v>
+        <v>-0.9653</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0178</v>
+        <v>-1.0475</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5825</v>
@@ -1078,13 +1078,13 @@
         <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8248</v>
+        <v>0.4813</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6778</v>
+        <v>0.364</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1469</v>
+        <v>0.1173</v>
       </c>
       <c r="V8" t="n">
         <v>-2.117</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. MENDES KOVACS</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8904</v>
+        <v>-2.4238</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.262</v>
+        <v>-2.1478</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3717</v>
+        <v>-0.276</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5448</v>
+        <v>-1.2422</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3054</v>
+        <v>-1.784</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.711</v>
+        <v>0.5773</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.7505</v>
+        <v>-0.5669</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0395</v>
+        <v>1.1441</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1662</v>
+        <v>-1.8195</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-1.2171</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7211</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1123</v>
+        <v>-0.5976</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9336</v>
+        <v>-0.4457</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1787</v>
+        <v>-0.1519</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4579</v>
+        <v>-1.4053</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4579</v>
+        <v>-1.0472</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3581</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>K. MENDES KOVACS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8958</v>
+        <v>-2.471</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9459</v>
+        <v>-3.5759</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>1.1049</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2422</v>
+        <v>-2.5448</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.784</v>
+        <v>-3.3054</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5773</v>
+        <v>-2.711</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5669</v>
+        <v>-2.7505</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1441</v>
+        <v>0.0395</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8195</v>
+        <v>0.1662</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2171</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.7211</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0697</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2438</v>
+        <v>0.6198</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1742</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4053</v>
+        <v>-0.4579</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0472</v>
+        <v>-0.4579</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1911</v>
+        <v>-2.7884</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3169</v>
+        <v>-2.0031</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8742</v>
+        <v>-0.7853</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0261</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3437</v>
+        <v>0.0591</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2635</v>
+        <v>0.0503</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0405</v>
+        <v>-3.2161</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0087</v>
+        <v>-4.629</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9681999999999999</v>
+        <v>1.4128</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0531</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.154</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1513</v>
+        <v>0.2284</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.3824</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5983000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2505</v>
+        <v>-2.921000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2936000000000005</v>
+        <v>0.03580000000000094</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9567</v>
+        <v>-2.956900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>2.302599999999999</v>
@@ -1441,13 +1441,13 @@
         <v>9.406699999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>9.331399999999999</v>
+        <v>9.3314</v>
       </c>
       <c r="K13" t="n">
         <v>2.0322</v>
       </c>
       <c r="L13" t="n">
-        <v>7.299299999999999</v>
+        <v>7.299300000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-7.0287</v>
@@ -1468,19 +1468,19 @@
         <v>15.4007</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9495000000000001</v>
+        <v>-0.6199999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2769</v>
+        <v>1.6062</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2264</v>
+        <v>-2.2263</v>
       </c>
       <c r="V13" t="n">
         <v>-5.630299999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>3.472099999999999</v>
+        <v>3.4721</v>
       </c>
       <c r="X13" t="n">
         <v>-9.102500000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0567</v>
+        <v>6.7097</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4461</v>
+        <v>5.0277</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6106</v>
+        <v>1.6821</v>
       </c>
       <c r="G14" t="n">
         <v>5.0408</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7839</v>
+        <v>0.4369</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6042</v>
+        <v>0.1858</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1796</v>
+        <v>0.2511</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. VANACLOCHA SANCHEZ</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3213</v>
+        <v>3.4552</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7157</v>
+        <v>2.3718</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3944</v>
+        <v>1.0834</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4469</v>
+        <v>1.6531</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4332</v>
+        <v>2.5398</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9863</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2587</v>
+        <v>1.3521</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1798</v>
+        <v>2.5889</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0789</v>
+        <v>-1.2368</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8118</v>
+        <v>0.301</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.0492</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0653</v>
+        <v>0.3502</v>
       </c>
       <c r="P15" t="n">
+        <v>1.8481</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.0267</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9976</v>
+        <v>-0.3951</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0648</v>
+        <v>-0.3992</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0673</v>
+        <v>0.0041</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8768</v>
+        <v>0.3491</v>
       </c>
       <c r="W15" t="n">
         <v>1.4189</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4579</v>
+        <v>-1.0698</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. ANDRADE AMIEL</t>
+          <t>B. VANACLOCHA SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6527</v>
+        <v>3.1567</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1307</v>
+        <v>4.6696</v>
       </c>
       <c r="F16" t="n">
-        <v>1.522</v>
+        <v>-1.513</v>
       </c>
       <c r="G16" t="n">
-        <v>0.272</v>
+        <v>0.4469</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.012</v>
+        <v>2.4332</v>
       </c>
       <c r="I16" t="n">
-        <v>1.284</v>
+        <v>-1.9863</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1709</v>
+        <v>3.2587</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4073</v>
+        <v>3.1798</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2365</v>
+        <v>0.0789</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4428</v>
+        <v>-2.8118</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3953</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0475</v>
+        <v>-2.0653</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1487</v>
+        <v>0.833</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3016</v>
+        <v>1.0188</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1529</v>
+        <v>-0.1858</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.8768</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>F. ANDRADE AMIEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4161</v>
+        <v>2.1384</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8488</v>
+        <v>0.1893</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5673</v>
+        <v>1.9491</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6531</v>
+        <v>0.272</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5398</v>
+        <v>-1.012</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8866000000000001</v>
+        <v>1.284</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3521</v>
+        <v>-0.1709</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5889</v>
+        <v>-1.4073</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2368</v>
+        <v>1.2365</v>
       </c>
       <c r="M17" t="n">
-        <v>0.301</v>
+        <v>0.4428</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0492</v>
+        <v>0.3953</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3502</v>
+        <v>0.0475</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4342</v>
+        <v>0.6344</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9222</v>
+        <v>0.3602</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.512</v>
+        <v>0.2743</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9726</v>
+        <v>1.0057</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5877</v>
+        <v>2.2738</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6151</v>
+        <v>-1.2681</v>
       </c>
       <c r="G18" t="n">
         <v>1.5248</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.1133</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5384</v>
+        <v>0.2246</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4582</v>
+        <v>-0.1112</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6591</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2807</v>
+        <v>-0.538</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8472</v>
+        <v>-2.3242</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5666</v>
+        <v>1.7862</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7504</v>
@@ -1936,13 +1936,13 @@
         <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4152</v>
+        <v>0.3274</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5542</v>
+        <v>-0.0312</v>
       </c>
       <c r="U19" t="n">
-        <v>0.139</v>
+        <v>0.3586</v>
       </c>
       <c r="V19" t="n">
         <v>2.117</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0638</v>
+        <v>-2.7606</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1265</v>
+        <v>-2.2897</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.4709</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4965</v>
@@ -2014,13 +2014,13 @@
         <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>0.059</v>
+        <v>0.3623</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3566</v>
+        <v>0.4802</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4156</v>
+        <v>-0.1179</v>
       </c>
       <c r="V20" t="n">
         <v>1.6591</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.43</v>
+        <v>-2.9924</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3208</v>
+        <v>-2.1116</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1092</v>
+        <v>-0.8808</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9392</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2855</v>
+        <v>0.1521</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0931</v>
+        <v>0.1161</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1924</v>
+        <v>0.036</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3943</v>
+        <v>-5.5295</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4775</v>
+        <v>-4.8499</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.6796</v>
       </c>
       <c r="G22" t="n">
         <v>-7.0541</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9849</v>
+        <v>-0.1202</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3566</v>
+        <v>0.271</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6283</v>
+        <v>-0.3912</v>
       </c>
       <c r="V22" t="n">
         <v>2.4661</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.250599999999999</v>
+        <v>4.645199999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>2.957</v>
+        <v>2.9568</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2937000000000004</v>
+        <v>1.6884</v>
       </c>
       <c r="G23" t="n">
         <v>-2.302599999999999</v>
@@ -2230,7 +2230,7 @@
         <v>-2.1073</v>
       </c>
       <c r="M23" t="n">
-        <v>-9.331399999999999</v>
+        <v>-9.3314</v>
       </c>
       <c r="N23" t="n">
         <v>-2.0319</v>
@@ -2248,13 +2248,13 @@
         <v>14.3741</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9496000000000003</v>
+        <v>2.3441</v>
       </c>
       <c r="T23" t="n">
         <v>2.2263</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2769</v>
+        <v>0.118</v>
       </c>
       <c r="V23" t="n">
         <v>5.6304</v>
